--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G674"/>
+  <dimension ref="A1:G676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18634,6 +18634,60 @@
         <v>343.16</v>
       </c>
       <c r="G674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="C675" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="D675" t="n">
+        <v>352.01</v>
+      </c>
+      <c r="E675" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="F675" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="C676" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="D676" t="n">
+        <v>351.49</v>
+      </c>
+      <c r="E676" t="n">
+        <v>345.7</v>
+      </c>
+      <c r="F676" t="n">
+        <v>342.42</v>
+      </c>
+      <c r="G676" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18650,7 +18704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B734"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25993,6 +26047,26 @@
       </c>
       <c r="B734" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -26161,28 +26235,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5502290532821869</v>
+        <v>-0.5502926793198383</v>
       </c>
       <c r="J2" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="K2" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L2" t="n">
-        <v>0.135442286899207</v>
+        <v>0.1362725376615448</v>
       </c>
       <c r="M2" t="n">
-        <v>8.377753061659932</v>
+        <v>8.354393139730746</v>
       </c>
       <c r="N2" t="n">
-        <v>110.4455183680643</v>
+        <v>110.1190098616332</v>
       </c>
       <c r="O2" t="n">
-        <v>10.50930627434867</v>
+        <v>10.49376052050137</v>
       </c>
       <c r="P2" t="n">
-        <v>371.8747513495812</v>
+        <v>371.8754162422575</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26239,28 +26313,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5304754930121346</v>
+        <v>-0.5306060252305698</v>
       </c>
       <c r="J3" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="K3" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1284685586251628</v>
+        <v>0.1292921531014061</v>
       </c>
       <c r="M3" t="n">
-        <v>8.541759148069536</v>
+        <v>8.517306278834225</v>
       </c>
       <c r="N3" t="n">
-        <v>109.1033806175013</v>
+        <v>108.7805091776967</v>
       </c>
       <c r="O3" t="n">
-        <v>10.44525636916113</v>
+        <v>10.42978950783268</v>
       </c>
       <c r="P3" t="n">
-        <v>372.102001413426</v>
+        <v>372.1033634801633</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26317,28 +26391,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.584394293775122</v>
+        <v>-0.5848476449138149</v>
       </c>
       <c r="J4" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="K4" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1561220598229978</v>
+        <v>0.1572293232032668</v>
       </c>
       <c r="M4" t="n">
-        <v>8.207470493642269</v>
+        <v>8.185379435084942</v>
       </c>
       <c r="N4" t="n">
-        <v>105.4990732211016</v>
+        <v>105.1883891820304</v>
       </c>
       <c r="O4" t="n">
-        <v>10.2712741770971</v>
+        <v>10.25613909724466</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2416089049666</v>
+        <v>368.2463373273509</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26395,28 +26469,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4696664782689379</v>
+        <v>-0.4722837772454781</v>
       </c>
       <c r="J5" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="K5" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0977997975892313</v>
+        <v>0.09935200013002199</v>
       </c>
       <c r="M5" t="n">
-        <v>8.56806902612675</v>
+        <v>8.555537802572227</v>
       </c>
       <c r="N5" t="n">
-        <v>116.2961780092127</v>
+        <v>116.0088101607464</v>
       </c>
       <c r="O5" t="n">
-        <v>10.78407056770367</v>
+        <v>10.77073860794822</v>
       </c>
       <c r="P5" t="n">
-        <v>362.8243591643903</v>
+        <v>362.8516534792099</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26473,28 +26547,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3805070740289442</v>
+        <v>-0.3832698425012224</v>
       </c>
       <c r="J6" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="K6" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06907024186796118</v>
+        <v>0.07041592331680291</v>
       </c>
       <c r="M6" t="n">
-        <v>8.160157279654779</v>
+        <v>8.149398496089001</v>
       </c>
       <c r="N6" t="n">
-        <v>111.5251346658497</v>
+        <v>111.2585860483403</v>
       </c>
       <c r="O6" t="n">
-        <v>10.5605461348289</v>
+        <v>10.5479185647378</v>
       </c>
       <c r="P6" t="n">
-        <v>357.5558016907241</v>
+        <v>357.5846134834461</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26532,7 +26606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G674"/>
+  <dimension ref="A1:G676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51473,6 +51547,80 @@
         </is>
       </c>
     </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-40.92651330857677,176.1863767820095</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-40.926907362434115,176.18564550054722</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-40.92725551770368,176.18486931458995</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-40.92760179104725,176.1840912901601</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-40.9279712630225,176.1833359655078</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-40.92650615315277,176.18636978113648</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-40.926903025794914,176.18564125759715</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-40.92725175926524,176.1848656373747</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-40.92760070687717,176.1840902294273</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-40.92796779366247,176.18333257116836</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G676"/>
+  <dimension ref="A1:G678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18688,6 +18688,60 @@
         <v>342.42</v>
       </c>
       <c r="G676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="C677" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="D677" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="E677" t="n">
+        <v>345.27</v>
+      </c>
+      <c r="F677" t="n">
+        <v>341.88</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="C678" t="n">
+        <v>356.29</v>
+      </c>
+      <c r="D678" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="E678" t="n">
+        <v>345.09</v>
+      </c>
+      <c r="F678" t="n">
+        <v>341.61</v>
+      </c>
+      <c r="G678" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18704,7 +18758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B736"/>
+  <dimension ref="A1:B738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26067,6 +26121,26 @@
       </c>
       <c r="B736" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>
@@ -26235,28 +26309,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5502926793198383</v>
+        <v>-0.5511381216808316</v>
       </c>
       <c r="J2" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="K2" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1362725376615448</v>
+        <v>0.1374320358907252</v>
       </c>
       <c r="M2" t="n">
-        <v>8.354393139730746</v>
+        <v>8.334162852900928</v>
       </c>
       <c r="N2" t="n">
-        <v>110.1190098616332</v>
+        <v>109.7997754927731</v>
       </c>
       <c r="O2" t="n">
-        <v>10.49376052050137</v>
+        <v>10.47853880523297</v>
       </c>
       <c r="P2" t="n">
-        <v>371.8754162422575</v>
+        <v>371.8842454202214</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26313,28 +26387,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5306060252305698</v>
+        <v>-0.5313970840493492</v>
       </c>
       <c r="J3" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="K3" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1292921531014061</v>
+        <v>0.1303915885212732</v>
       </c>
       <c r="M3" t="n">
-        <v>8.517306278834225</v>
+        <v>8.495986159120839</v>
       </c>
       <c r="N3" t="n">
-        <v>108.7805091776967</v>
+        <v>108.4645188061</v>
       </c>
       <c r="O3" t="n">
-        <v>10.42978950783268</v>
+        <v>10.41463003692882</v>
       </c>
       <c r="P3" t="n">
-        <v>372.1033634801633</v>
+        <v>372.1116247355337</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26391,28 +26465,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5848476449138149</v>
+        <v>-0.5855993384473298</v>
       </c>
       <c r="J4" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="K4" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1572293232032668</v>
+        <v>0.1584688463605948</v>
       </c>
       <c r="M4" t="n">
-        <v>8.185379435084942</v>
+        <v>8.16486984620545</v>
       </c>
       <c r="N4" t="n">
-        <v>105.1883891820304</v>
+        <v>104.882410732959</v>
       </c>
       <c r="O4" t="n">
-        <v>10.25613909724466</v>
+        <v>10.24121138991667</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2463373273509</v>
+        <v>368.2541874140399</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26469,28 +26543,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4722837772454781</v>
+        <v>-0.4751992289375506</v>
       </c>
       <c r="J5" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="K5" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09935200013002199</v>
+        <v>0.1010187235106058</v>
       </c>
       <c r="M5" t="n">
-        <v>8.555537802572227</v>
+        <v>8.544571227043907</v>
       </c>
       <c r="N5" t="n">
-        <v>116.0088101607464</v>
+        <v>115.7378549517468</v>
       </c>
       <c r="O5" t="n">
-        <v>10.77073860794822</v>
+        <v>10.75815295260979</v>
       </c>
       <c r="P5" t="n">
-        <v>362.8516534792099</v>
+        <v>362.8821001884839</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26547,28 +26621,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3832698425012224</v>
+        <v>-0.386519106157873</v>
       </c>
       <c r="J6" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="K6" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07041592331680291</v>
+        <v>0.0719285034018009</v>
       </c>
       <c r="M6" t="n">
-        <v>8.149398496089001</v>
+        <v>8.141063803574841</v>
       </c>
       <c r="N6" t="n">
-        <v>111.2585860483403</v>
+        <v>111.019060512143</v>
       </c>
       <c r="O6" t="n">
-        <v>10.5479185647378</v>
+        <v>10.53655828589882</v>
       </c>
       <c r="P6" t="n">
-        <v>357.5846134834461</v>
+        <v>357.6185462770591</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26606,7 +26680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G676"/>
+  <dimension ref="A1:G678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51621,6 +51695,80 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-40.9265008769307,176.18636461887755</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-40.92689818321425,176.18563651963694</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-40.927249590935304,176.1848635159046</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-40.927597598922894,176.18408718866021</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-40.927963890632306,176.18332875253694</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-40.92649907000528,176.18636285098086</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-40.92689565350785,176.1856340445834</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-40.92724995232363,176.18486386948294</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-40.92759629791874,176.18408591578103</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-40.92796193911717,176.18332684322138</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G678"/>
+  <dimension ref="A1:G684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18742,6 +18742,168 @@
         <v>341.61</v>
       </c>
       <c r="G678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="C679" t="n">
+        <v>353.38</v>
+      </c>
+      <c r="D679" t="n">
+        <v>348.96</v>
+      </c>
+      <c r="E679" t="n">
+        <v>342.94</v>
+      </c>
+      <c r="F679" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="C680" t="n">
+        <v>351.84</v>
+      </c>
+      <c r="D680" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="E680" t="n">
+        <v>341.78</v>
+      </c>
+      <c r="F680" t="n">
+        <v>338.21</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="C681" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="D681" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="E681" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="F681" t="n">
+        <v>337.55</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="C682" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="D682" t="n">
+        <v>346.97</v>
+      </c>
+      <c r="E682" t="n">
+        <v>341.12</v>
+      </c>
+      <c r="F682" t="n">
+        <v>337.72</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="C683" t="n">
+        <v>350.81</v>
+      </c>
+      <c r="D683" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="E683" t="n">
+        <v>341.32</v>
+      </c>
+      <c r="F683" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="C684" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="D684" t="n">
+        <v>345.6</v>
+      </c>
+      <c r="E684" t="n">
+        <v>339.75</v>
+      </c>
+      <c r="F684" t="n">
+        <v>336.23</v>
+      </c>
+      <c r="G684" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18758,7 +18920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B738"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26141,6 +26303,66 @@
       </c>
       <c r="B738" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -26309,28 +26531,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5511381216808316</v>
+        <v>-0.5599323594035847</v>
       </c>
       <c r="J2" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K2" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1374320358907252</v>
+        <v>0.1434461690046763</v>
       </c>
       <c r="M2" t="n">
-        <v>8.334162852900928</v>
+        <v>8.306705428850202</v>
       </c>
       <c r="N2" t="n">
-        <v>109.7997754927731</v>
+        <v>109.0661025121993</v>
       </c>
       <c r="O2" t="n">
-        <v>10.47853880523297</v>
+        <v>10.44347176527994</v>
       </c>
       <c r="P2" t="n">
-        <v>371.8842454202214</v>
+        <v>371.9765054107978</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26387,28 +26609,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5313970840493492</v>
+        <v>-0.5425491286058953</v>
       </c>
       <c r="J3" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K3" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1303915885212732</v>
+        <v>0.1371643956514359</v>
       </c>
       <c r="M3" t="n">
-        <v>8.495986159120839</v>
+        <v>8.475159587409747</v>
       </c>
       <c r="N3" t="n">
-        <v>108.4645188061</v>
+        <v>107.8742418437287</v>
       </c>
       <c r="O3" t="n">
-        <v>10.41463003692882</v>
+        <v>10.38625254091815</v>
       </c>
       <c r="P3" t="n">
-        <v>372.1116247355337</v>
+        <v>372.2286442112919</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26465,28 +26687,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5855993384473298</v>
+        <v>-0.5953903346558113</v>
       </c>
       <c r="J4" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K4" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1584688463605948</v>
+        <v>0.1653526678173909</v>
       </c>
       <c r="M4" t="n">
-        <v>8.16486984620545</v>
+        <v>8.14038513534622</v>
       </c>
       <c r="N4" t="n">
-        <v>104.882410732959</v>
+        <v>104.2433395916069</v>
       </c>
       <c r="O4" t="n">
-        <v>10.24121138991667</v>
+        <v>10.20996276151911</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2541874140399</v>
+        <v>368.3569285126945</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26543,28 +26765,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4751992289375506</v>
+        <v>-0.4903776243166685</v>
       </c>
       <c r="J5" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K5" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1010187235106058</v>
+        <v>0.108268628365901</v>
       </c>
       <c r="M5" t="n">
-        <v>8.544571227043907</v>
+        <v>8.543046602430964</v>
       </c>
       <c r="N5" t="n">
-        <v>115.7378549517468</v>
+        <v>115.38401686409</v>
       </c>
       <c r="O5" t="n">
-        <v>10.75815295260979</v>
+        <v>10.74169525094107</v>
       </c>
       <c r="P5" t="n">
-        <v>362.8821001884839</v>
+        <v>363.0413660219148</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26621,28 +26843,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.386519106157873</v>
+        <v>-0.4028530126997954</v>
       </c>
       <c r="J6" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K6" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0719285034018009</v>
+        <v>0.07861517511510718</v>
       </c>
       <c r="M6" t="n">
-        <v>8.141063803574841</v>
+        <v>8.14898169977414</v>
       </c>
       <c r="N6" t="n">
-        <v>111.019060512143</v>
+        <v>110.810484356129</v>
       </c>
       <c r="O6" t="n">
-        <v>10.53655828589882</v>
+        <v>10.52665589615852</v>
       </c>
       <c r="P6" t="n">
-        <v>357.6185462770591</v>
+        <v>357.789937458582</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26680,7 +26902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G678"/>
+  <dimension ref="A1:G684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51769,6 +51991,228 @@
         </is>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-40.92648085619525,176.1863450305876</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-40.92687462080366,176.1856134662883</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-40.92723347301472,176.18484774631438</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-40.92758075814571,176.18407071195043</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-40.927946688386506,176.18331192227788</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-40.92646394336882,176.1863284830885</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-40.92686349009253,176.18560257606185</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-40.927217065980905,176.18483169386954</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-40.92757237389513,176.18406250895646</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-40.92793736447898,176.1833027999983</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-40.92646285921319,176.18632742235167</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-40.926854744532946,176.18559401945802</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-40.9272138857626,176.18482858238337</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-40.92756449559007,176.18405480097263</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-40.92793259410737,176.18329813278652</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-40.92646921959275,176.1863336453416</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-40.926853877204685,176.18559317086934</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-40.927219089756136,176.18483367390635</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-40.92756760354535,176.18405784173666</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-40.92793382283947,176.1832993349471</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-40.92648100074931,176.18634517201926</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-40.92685604552532,176.18559529234108</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-40.92721280159725,176.18482752164954</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-40.92756904910591,176.18405925604563</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-40.92793006436475,176.18329565775028</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-40.92648085619525,176.1863450305876</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-40.926854816810305,176.18559409017374</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-40.92720918771267,176.18482398587028</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-40.92755770145497,176.18404815372205</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-40.92792305336351,176.183288798365</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
